--- a/output/upload/S00028_1726_e정기보험_무배당.xlsx
+++ b/output/upload/S00028_1726_e정기보험_무배당.xlsx
@@ -725,17 +725,9 @@
     </row>
     <row r="7">
       <c r="A7" s="5" t="n"/>
-      <c r="B7" s="5" t="inlineStr">
-        <is>
-          <t>1726041</t>
-        </is>
-      </c>
+      <c r="B7" s="5" t="inlineStr"/>
       <c r="C7" s="5" t="n"/>
-      <c r="D7" s="5" t="inlineStr">
-        <is>
-          <t>1726041</t>
-        </is>
-      </c>
+      <c r="D7" s="5" t="inlineStr"/>
       <c r="E7" s="5" t="n"/>
       <c r="F7" s="5" t="n"/>
       <c r="G7" s="6" t="inlineStr">
@@ -768,16 +760,8 @@
       </c>
     </row>
     <row r="8">
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>1726041</t>
-        </is>
-      </c>
-      <c r="D8" t="inlineStr">
-        <is>
-          <t>1726041</t>
-        </is>
-      </c>
+      <c r="B8" t="inlineStr"/>
+      <c r="D8" t="inlineStr"/>
       <c r="G8" t="inlineStr">
         <is>
           <t>20260101</t>

--- a/output/upload/S00028_1726_e정기보험_무배당.xlsx
+++ b/output/upload/S00028_1726_e정기보험_무배당.xlsx
@@ -725,11 +725,31 @@
     </row>
     <row r="7">
       <c r="A7" s="5" t="n"/>
-      <c r="B7" s="5" t="inlineStr"/>
-      <c r="C7" s="5" t="n"/>
-      <c r="D7" s="5" t="inlineStr"/>
-      <c r="E7" s="5" t="n"/>
-      <c r="F7" s="5" t="n"/>
+      <c r="B7" s="5" t="inlineStr">
+        <is>
+          <t>1726039</t>
+        </is>
+      </c>
+      <c r="C7" s="5" t="inlineStr">
+        <is>
+          <t>한화생명 e정기보험 무배당 순수보장형 해약환급금 미지급형(납입기간중 0%, 납입기간후 50%) 표준체</t>
+        </is>
+      </c>
+      <c r="D7" s="5" t="inlineStr">
+        <is>
+          <t>172639</t>
+        </is>
+      </c>
+      <c r="E7" s="5" t="inlineStr">
+        <is>
+          <t>한화생명 e정기보험 무배당 순수보장형 해약환급금 미지급형(납입기간중 0%, 납입기간후 50%) 표준체</t>
+        </is>
+      </c>
+      <c r="F7" s="5" t="inlineStr">
+        <is>
+          <t>S00028</t>
+        </is>
+      </c>
       <c r="G7" s="6" t="inlineStr">
         <is>
           <t>20260101</t>
@@ -760,8 +780,31 @@
       </c>
     </row>
     <row r="8">
-      <c r="B8" t="inlineStr"/>
-      <c r="D8" t="inlineStr"/>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>1726039</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>한화생명 e정기보험 무배당 순수보장형 해약환급금 미지급형(납입기간중 0%, 납입기간후 50%) 표준체</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>172639</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>한화생명 e정기보험 무배당 순수보장형 해약환급금 미지급형(납입기간중 0%, 납입기간후 50%) 표준체</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>S00028</t>
+        </is>
+      </c>
       <c r="G8" t="inlineStr">
         <is>
           <t>20260101</t>

--- a/output/upload/S00028_1726_e정기보험_무배당.xlsx
+++ b/output/upload/S00028_1726_e정기보험_무배당.xlsx
@@ -737,7 +737,7 @@
       </c>
       <c r="D7" s="5" t="inlineStr">
         <is>
-          <t>172639</t>
+          <t>1726039</t>
         </is>
       </c>
       <c r="E7" s="5" t="inlineStr">
@@ -792,7 +792,7 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>172639</t>
+          <t>1726039</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">

--- a/output/upload/S00028_1726_e정기보험_무배당.xlsx
+++ b/output/upload/S00028_1726_e정기보험_무배당.xlsx
@@ -499,7 +499,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M8"/>
+  <dimension ref="A1:M14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="17.484375" customWidth="1" min="1" max="1"/>
@@ -834,6 +834,336 @@
         </is>
       </c>
     </row>
+    <row r="9">
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>1726040</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>한화생명 e정기보험 무배당 순수보장형 해약환급금 미지급형(납입기간중 0%, 납입기간후 50%) 건강체</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>1726040</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>한화생명 e정기보험 무배당 순수보장형 해약환급금 미지급형(납입기간중 0%, 납입기간후 50%) 건강체</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>S00028</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>20260101</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>99991231</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>M1</t>
+        </is>
+      </c>
+      <c r="J9" t="n">
+        <v>1</v>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="L9" t="inlineStr">
+        <is>
+          <t>1,2,3,4,7</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>1726040</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>한화생명 e정기보험 무배당 순수보장형 해약환급금 미지급형(납입기간중 0%, 납입기간후 50%) 건강체</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>1726040</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>한화생명 e정기보험 무배당 순수보장형 해약환급금 미지급형(납입기간중 0%, 납입기간후 50%) 건강체</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>S00028</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>20260101</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>99991231</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>M12</t>
+        </is>
+      </c>
+      <c r="J10" t="n">
+        <v>12</v>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="L10" t="inlineStr">
+        <is>
+          <t>1,2,3,4,7</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>1726041</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>한화생명 e정기보험 무배당 만기환급형 표준형 표준체</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>1726041</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>한화생명 e정기보험 무배당 만기환급형 표준형 표준체</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>S00028</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>20260101</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>99991231</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>M1</t>
+        </is>
+      </c>
+      <c r="J11" t="n">
+        <v>1</v>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="L11" t="inlineStr">
+        <is>
+          <t>1,2,3,4,7</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>1726041</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>한화생명 e정기보험 무배당 만기환급형 표준형 표준체</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>1726041</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>한화생명 e정기보험 무배당 만기환급형 표준형 표준체</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>S00028</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>20260101</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>99991231</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>M12</t>
+        </is>
+      </c>
+      <c r="J12" t="n">
+        <v>12</v>
+      </c>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="L12" t="inlineStr">
+        <is>
+          <t>1,2,3,4,7</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>1726042</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>한화생명 e정기보험 무배당 만기환급형 표준형 건강체</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>1726042</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>한화생명 e정기보험 무배당 만기환급형 표준형 건강체</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>S00028</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>20260101</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>99991231</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>M1</t>
+        </is>
+      </c>
+      <c r="J13" t="n">
+        <v>1</v>
+      </c>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="L13" t="inlineStr">
+        <is>
+          <t>1,2,3,4,7</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>1726042</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>한화생명 e정기보험 무배당 만기환급형 표준형 건강체</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>1726042</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>한화생명 e정기보험 무배당 만기환급형 표준형 건강체</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>S00028</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>20260101</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>99991231</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>M12</t>
+        </is>
+      </c>
+      <c r="J14" t="n">
+        <v>12</v>
+      </c>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="L14" t="inlineStr">
+        <is>
+          <t>1,2,3,4,7</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <mergeCells count="5">
     <mergeCell ref="A3:F3"/>

--- a/output/upload/S00028_1726_e정기보험_무배당.xlsx
+++ b/output/upload/S00028_1726_e정기보험_무배당.xlsx
@@ -1,12 +1,12 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="세트속성값" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="세트속성값" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
 </workbook>
@@ -499,7 +499,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M14"/>
+  <dimension ref="A1:M10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="17.484375" customWidth="1" min="1" max="1"/>
@@ -760,11 +760,7 @@
           <t>99991231</t>
         </is>
       </c>
-      <c r="I7" s="6" t="inlineStr">
-        <is>
-          <t>M1</t>
-        </is>
-      </c>
+      <c r="I7" s="6" t="n"/>
       <c r="J7" s="6" t="n">
         <v>1</v>
       </c>
@@ -782,22 +778,22 @@
     <row r="8">
       <c r="B8" t="inlineStr">
         <is>
-          <t>1726039</t>
+          <t>1726040</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>한화생명 e정기보험 무배당 순수보장형 해약환급금 미지급형(납입기간중 0%, 납입기간후 50%) 표준체</t>
+          <t>한화생명 e정기보험 무배당 순수보장형 해약환급금 미지급형(납입기간중 0%, 납입기간후 50%) 건강체</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>1726039</t>
+          <t>1726040</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>한화생명 e정기보험 무배당 순수보장형 해약환급금 미지급형(납입기간중 0%, 납입기간후 50%) 표준체</t>
+          <t>한화생명 e정기보험 무배당 순수보장형 해약환급금 미지급형(납입기간중 0%, 납입기간후 50%) 건강체</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -815,13 +811,8 @@
           <t>99991231</t>
         </is>
       </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>M12</t>
-        </is>
-      </c>
       <c r="J8" t="n">
-        <v>12</v>
+        <v>1</v>
       </c>
       <c r="K8" t="inlineStr">
         <is>
@@ -837,22 +828,22 @@
     <row r="9">
       <c r="B9" t="inlineStr">
         <is>
-          <t>1726040</t>
+          <t>1726041</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>한화생명 e정기보험 무배당 순수보장형 해약환급금 미지급형(납입기간중 0%, 납입기간후 50%) 건강체</t>
+          <t>한화생명 e정기보험 무배당 만기환급형 표준형 표준체</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>1726040</t>
+          <t>1726041</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>한화생명 e정기보험 무배당 순수보장형 해약환급금 미지급형(납입기간중 0%, 납입기간후 50%) 건강체</t>
+          <t>한화생명 e정기보험 무배당 만기환급형 표준형 표준체</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -868,11 +859,6 @@
       <c r="H9" t="inlineStr">
         <is>
           <t>99991231</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>M1</t>
         </is>
       </c>
       <c r="J9" t="n">
@@ -892,22 +878,22 @@
     <row r="10">
       <c r="B10" t="inlineStr">
         <is>
-          <t>1726040</t>
+          <t>1726042</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>한화생명 e정기보험 무배당 순수보장형 해약환급금 미지급형(납입기간중 0%, 납입기간후 50%) 건강체</t>
+          <t>한화생명 e정기보험 무배당 만기환급형 표준형 건강체</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>1726040</t>
+          <t>1726042</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>한화생명 e정기보험 무배당 순수보장형 해약환급금 미지급형(납입기간중 0%, 납입기간후 50%) 건강체</t>
+          <t>한화생명 e정기보험 무배당 만기환급형 표준형 건강체</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -925,13 +911,8 @@
           <t>99991231</t>
         </is>
       </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>M12</t>
-        </is>
-      </c>
       <c r="J10" t="n">
-        <v>12</v>
+        <v>1</v>
       </c>
       <c r="K10" t="inlineStr">
         <is>
@@ -939,226 +920,6 @@
         </is>
       </c>
       <c r="L10" t="inlineStr">
-        <is>
-          <t>1,2,3,4,7</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>1726041</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>한화생명 e정기보험 무배당 만기환급형 표준형 표준체</t>
-        </is>
-      </c>
-      <c r="D11" t="inlineStr">
-        <is>
-          <t>1726041</t>
-        </is>
-      </c>
-      <c r="E11" t="inlineStr">
-        <is>
-          <t>한화생명 e정기보험 무배당 만기환급형 표준형 표준체</t>
-        </is>
-      </c>
-      <c r="F11" t="inlineStr">
-        <is>
-          <t>S00028</t>
-        </is>
-      </c>
-      <c r="G11" t="inlineStr">
-        <is>
-          <t>20260101</t>
-        </is>
-      </c>
-      <c r="H11" t="inlineStr">
-        <is>
-          <t>99991231</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>M1</t>
-        </is>
-      </c>
-      <c r="J11" t="n">
-        <v>1</v>
-      </c>
-      <c r="K11" t="inlineStr">
-        <is>
-          <t>M</t>
-        </is>
-      </c>
-      <c r="L11" t="inlineStr">
-        <is>
-          <t>1,2,3,4,7</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>1726041</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>한화생명 e정기보험 무배당 만기환급형 표준형 표준체</t>
-        </is>
-      </c>
-      <c r="D12" t="inlineStr">
-        <is>
-          <t>1726041</t>
-        </is>
-      </c>
-      <c r="E12" t="inlineStr">
-        <is>
-          <t>한화생명 e정기보험 무배당 만기환급형 표준형 표준체</t>
-        </is>
-      </c>
-      <c r="F12" t="inlineStr">
-        <is>
-          <t>S00028</t>
-        </is>
-      </c>
-      <c r="G12" t="inlineStr">
-        <is>
-          <t>20260101</t>
-        </is>
-      </c>
-      <c r="H12" t="inlineStr">
-        <is>
-          <t>99991231</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>M12</t>
-        </is>
-      </c>
-      <c r="J12" t="n">
-        <v>12</v>
-      </c>
-      <c r="K12" t="inlineStr">
-        <is>
-          <t>M</t>
-        </is>
-      </c>
-      <c r="L12" t="inlineStr">
-        <is>
-          <t>1,2,3,4,7</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>1726042</t>
-        </is>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>한화생명 e정기보험 무배당 만기환급형 표준형 건강체</t>
-        </is>
-      </c>
-      <c r="D13" t="inlineStr">
-        <is>
-          <t>1726042</t>
-        </is>
-      </c>
-      <c r="E13" t="inlineStr">
-        <is>
-          <t>한화생명 e정기보험 무배당 만기환급형 표준형 건강체</t>
-        </is>
-      </c>
-      <c r="F13" t="inlineStr">
-        <is>
-          <t>S00028</t>
-        </is>
-      </c>
-      <c r="G13" t="inlineStr">
-        <is>
-          <t>20260101</t>
-        </is>
-      </c>
-      <c r="H13" t="inlineStr">
-        <is>
-          <t>99991231</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr">
-        <is>
-          <t>M1</t>
-        </is>
-      </c>
-      <c r="J13" t="n">
-        <v>1</v>
-      </c>
-      <c r="K13" t="inlineStr">
-        <is>
-          <t>M</t>
-        </is>
-      </c>
-      <c r="L13" t="inlineStr">
-        <is>
-          <t>1,2,3,4,7</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>1726042</t>
-        </is>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>한화생명 e정기보험 무배당 만기환급형 표준형 건강체</t>
-        </is>
-      </c>
-      <c r="D14" t="inlineStr">
-        <is>
-          <t>1726042</t>
-        </is>
-      </c>
-      <c r="E14" t="inlineStr">
-        <is>
-          <t>한화생명 e정기보험 무배당 만기환급형 표준형 건강체</t>
-        </is>
-      </c>
-      <c r="F14" t="inlineStr">
-        <is>
-          <t>S00028</t>
-        </is>
-      </c>
-      <c r="G14" t="inlineStr">
-        <is>
-          <t>20260101</t>
-        </is>
-      </c>
-      <c r="H14" t="inlineStr">
-        <is>
-          <t>99991231</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr">
-        <is>
-          <t>M12</t>
-        </is>
-      </c>
-      <c r="J14" t="n">
-        <v>12</v>
-      </c>
-      <c r="K14" t="inlineStr">
-        <is>
-          <t>M</t>
-        </is>
-      </c>
-      <c r="L14" t="inlineStr">
         <is>
           <t>1,2,3,4,7</t>
         </is>
